--- a/Excel/Grade Book.xlsx
+++ b/Excel/Grade Book.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\j-l-data-science-data-analytics\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Tests\j-l-data-science-data-analytics\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7595D284-73C5-4278-9572-DDF04F7D8383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95E668E0-8D72-4B1E-8DF6-9187BD05B6CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -198,15 +198,14 @@
     </font>
     <font>
       <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="9" tint="-0.249977111117893"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <i/>
       <sz val="11"/>
       <color theme="9" tint="-0.249977111117893"/>
       <name val="Calibri"/>
@@ -279,12 +278,12 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -576,55 +575,55 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="17"/>
                 <c:pt idx="0">
-                  <c:v>5</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>9</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>6</c:v>
                 </c:pt>
-                <c:pt idx="10">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="13">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>6</c:v>
                 </c:pt>
-                <c:pt idx="12">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>8</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -971,55 +970,55 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="17"/>
                 <c:pt idx="0">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>20</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="8">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>17</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>19</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1389,55 +1388,55 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="17"/>
                 <c:pt idx="0">
-                  <c:v>80</c:v>
+                  <c:v>82</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>74</c:v>
+                  <c:v>77</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>54</c:v>
+                  <c:v>93</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>95</c:v>
+                  <c:v>97</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>93</c:v>
+                  <c:v>85</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>53</c:v>
+                  <c:v>94</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>59</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>56</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>80</c:v>
-                </c:pt>
                 <c:pt idx="9">
-                  <c:v>60</c:v>
+                  <c:v>98</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>69</c:v>
+                  <c:v>55</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>97</c:v>
+                  <c:v>71</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>95</c:v>
+                  <c:v>78</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>83</c:v>
+                  <c:v>57</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>84</c:v>
+                  <c:v>76</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>64</c:v>
+                  <c:v>79</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>89</c:v>
+                  <c:v>65</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3791,21 +3790,21 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:M24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="132" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="132" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3840,7 +3839,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>24</v>
       </c>
@@ -3857,7 +3856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -3865,7 +3864,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3874,15 +3873,15 @@
       </c>
       <c r="C4">
         <f ca="1">RANDBETWEEN(5, 10)</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D4">
         <f ca="1">RANDBETWEEN(10, 20)</f>
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E4">
         <f ca="1">RANDBETWEEN(50, 100)</f>
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F4">
         <f ca="1">RANDBETWEEN(0, 1)</f>
@@ -3890,15 +3889,15 @@
       </c>
       <c r="H4" s="1">
         <f ca="1">C4/C$2</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I4" s="1">
         <f ca="1">D4/D$2</f>
-        <v>1</v>
+        <v>0.65</v>
       </c>
       <c r="J4" s="1">
         <f t="shared" ref="J4:K19" ca="1" si="0">E4/E$2</f>
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="K4" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -3909,7 +3908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -3918,42 +3917,42 @@
       </c>
       <c r="C5">
         <f t="shared" ref="C5:C20" ca="1" si="1">RANDBETWEEN(5, 10)</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D5">
         <f t="shared" ref="D5:D20" ca="1" si="2">RANDBETWEEN(10, 20)</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E5">
         <f t="shared" ref="E5:E20" ca="1" si="3">RANDBETWEEN(50, 100)</f>
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F5">
         <f t="shared" ref="F5:F20" ca="1" si="4">RANDBETWEEN(0, 1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" s="1">
         <f t="shared" ref="H5:I20" ca="1" si="5">C5/C$2</f>
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I5" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="J5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.74</v>
+        <v>0.77</v>
       </c>
       <c r="K5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" s="1" t="b">
         <f t="shared" ref="M5:M20" ca="1" si="6">OR(H5&lt;0.5, I5&lt;0.5, J5&lt;0.5, K5&lt;0.5)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -3962,15 +3961,15 @@
       </c>
       <c r="C6">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D6">
         <f t="shared" ca="1" si="2"/>
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E6">
         <f t="shared" ca="1" si="3"/>
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="F6">
         <f t="shared" ca="1" si="4"/>
@@ -3978,15 +3977,15 @@
       </c>
       <c r="H6" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="I6" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="J6" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.54</v>
+        <v>0.93</v>
       </c>
       <c r="K6" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -3997,7 +3996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -4006,15 +4005,15 @@
       </c>
       <c r="C7">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7">
         <f t="shared" ca="1" si="2"/>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E7">
         <f t="shared" ca="1" si="3"/>
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F7">
         <f t="shared" ca="1" si="4"/>
@@ -4022,15 +4021,15 @@
       </c>
       <c r="H7" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I7" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J7" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="K7" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -4041,7 +4040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -4050,15 +4049,15 @@
       </c>
       <c r="C8">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D8">
         <f t="shared" ca="1" si="2"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E8">
         <f t="shared" ca="1" si="3"/>
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="F8">
         <f t="shared" ca="1" si="4"/>
@@ -4066,15 +4065,15 @@
       </c>
       <c r="H8" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I8" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="J8" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.93</v>
+        <v>0.85</v>
       </c>
       <c r="K8" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -4085,7 +4084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -4098,11 +4097,11 @@
       </c>
       <c r="D9">
         <f t="shared" ca="1" si="2"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E9">
         <f t="shared" ca="1" si="3"/>
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="F9">
         <f t="shared" ca="1" si="4"/>
@@ -4114,11 +4113,11 @@
       </c>
       <c r="I9" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="J9" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.53</v>
+        <v>0.94</v>
       </c>
       <c r="K9" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -4129,7 +4128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -4138,15 +4137,15 @@
       </c>
       <c r="C10">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D10">
         <f t="shared" ca="1" si="2"/>
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E10">
         <f t="shared" ca="1" si="3"/>
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="F10">
         <f t="shared" ca="1" si="4"/>
@@ -4154,15 +4153,15 @@
       </c>
       <c r="H10" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="I10" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.9</v>
+        <v>0.65</v>
       </c>
       <c r="J10" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.59</v>
+        <v>0.67</v>
       </c>
       <c r="K10" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -4173,7 +4172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -4182,15 +4181,15 @@
       </c>
       <c r="C11">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D11">
         <f t="shared" ca="1" si="2"/>
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E11">
         <f t="shared" ca="1" si="3"/>
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="F11">
         <f t="shared" ca="1" si="4"/>
@@ -4198,15 +4197,15 @@
       </c>
       <c r="H11" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="I11" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="J11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.56000000000000005</v>
+        <v>0.69</v>
       </c>
       <c r="K11" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -4217,7 +4216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -4226,15 +4225,15 @@
       </c>
       <c r="C12">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12">
         <f t="shared" ca="1" si="2"/>
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E12">
         <f t="shared" ca="1" si="3"/>
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="F12">
         <f t="shared" ca="1" si="4"/>
@@ -4242,15 +4241,15 @@
       </c>
       <c r="H12" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I12" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.7</v>
+        <v>0.95</v>
       </c>
       <c r="J12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.8</v>
+        <v>0.59</v>
       </c>
       <c r="K12" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -4261,7 +4260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -4270,42 +4269,42 @@
       </c>
       <c r="C13">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D13">
         <f t="shared" ca="1" si="2"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E13">
         <f t="shared" ca="1" si="3"/>
-        <v>60</v>
+        <v>98</v>
       </c>
       <c r="F13">
         <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="I13" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.65</v>
+        <v>0.9</v>
       </c>
       <c r="J13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.6</v>
+        <v>0.98</v>
       </c>
       <c r="K13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" s="1" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -4314,42 +4313,42 @@
       </c>
       <c r="C14">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D14">
         <f t="shared" ca="1" si="2"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E14">
         <f t="shared" ca="1" si="3"/>
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="F14">
         <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="I14" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.55000000000000004</v>
+        <v>0.65</v>
       </c>
       <c r="J14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.69</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="K14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" s="1" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -4358,42 +4357,42 @@
       </c>
       <c r="C15">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D15">
         <f t="shared" ca="1" si="2"/>
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E15">
         <f t="shared" ca="1" si="3"/>
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="F15">
         <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="I15" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="J15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.97</v>
+        <v>0.71</v>
       </c>
       <c r="K15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="1" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -4402,15 +4401,15 @@
       </c>
       <c r="C16">
         <f t="shared" ca="1" si="1"/>
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D16">
         <f t="shared" ca="1" si="2"/>
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E16">
         <f t="shared" ca="1" si="3"/>
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="F16">
         <f t="shared" ca="1" si="4"/>
@@ -4418,15 +4417,15 @@
       </c>
       <c r="H16" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="I16" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.9</v>
+        <v>0.65</v>
       </c>
       <c r="J16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.95</v>
+        <v>0.78</v>
       </c>
       <c r="K16" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -4437,7 +4436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -4446,15 +4445,15 @@
       </c>
       <c r="C17">
         <f t="shared" ca="1" si="1"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17">
         <f t="shared" ca="1" si="2"/>
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E17">
         <f t="shared" ca="1" si="3"/>
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="F17">
         <f t="shared" ca="1" si="4"/>
@@ -4462,15 +4461,15 @@
       </c>
       <c r="H17" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="I17" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.7</v>
+        <v>0.95</v>
       </c>
       <c r="J17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.83</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="K17" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -4481,7 +4480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -4490,42 +4489,42 @@
       </c>
       <c r="C18">
         <f t="shared" ca="1" si="1"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D18">
         <f t="shared" ca="1" si="2"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E18">
         <f t="shared" ca="1" si="3"/>
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="F18">
         <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="I18" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.6</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="J18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.84</v>
+        <v>0.76</v>
       </c>
       <c r="K18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="1" t="b">
         <f t="shared" ca="1" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -4534,15 +4533,15 @@
       </c>
       <c r="C19">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D19">
         <f t="shared" ca="1" si="2"/>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E19">
         <f t="shared" ca="1" si="3"/>
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="F19">
         <f t="shared" ca="1" si="4"/>
@@ -4550,15 +4549,15 @@
       </c>
       <c r="H19" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="I19" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="J19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>0.64</v>
+        <v>0.79</v>
       </c>
       <c r="K19" s="1">
         <f t="shared" ca="1" si="0"/>
@@ -4569,7 +4568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -4578,15 +4577,15 @@
       </c>
       <c r="C20">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D20">
         <f t="shared" ca="1" si="2"/>
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E20">
         <f t="shared" ca="1" si="3"/>
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="F20">
         <f t="shared" ca="1" si="4"/>
@@ -4594,15 +4593,15 @@
       </c>
       <c r="H20" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="I20" s="1">
         <f t="shared" ca="1" si="5"/>
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="J20" s="1">
         <f t="shared" ref="J20" ca="1" si="7">E20/E$2</f>
-        <v>0.89</v>
+        <v>0.65</v>
       </c>
       <c r="K20" s="1">
         <f t="shared" ref="K20" ca="1" si="8">F20/F$2</f>
@@ -4613,7 +4612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -4627,7 +4626,7 @@
       </c>
       <c r="E22">
         <f t="shared" ca="1" si="9"/>
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F22">
         <f t="shared" ref="F22" ca="1" si="10">MAX(F4:F20)</f>
@@ -4643,28 +4642,28 @@
       </c>
       <c r="J22" s="1">
         <f t="shared" ca="1" si="11"/>
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="K22" s="1">
         <f t="shared" ca="1" si="11"/>
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>27</v>
       </c>
       <c r="C23">
         <f ca="1">MIN(C4:C20)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D23">
         <f t="shared" ref="D23:E23" ca="1" si="12">MIN(D4:D20)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E23">
         <f t="shared" ca="1" si="12"/>
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F23">
         <f t="shared" ref="F23" ca="1" si="13">MIN(F4:F20)</f>
@@ -4672,56 +4671,56 @@
       </c>
       <c r="H23" s="1">
         <f ca="1">MIN(H4:H20)</f>
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="I23" s="1">
         <f t="shared" ref="I23:K23" ca="1" si="14">MIN(I4:I20)</f>
-        <v>0.55000000000000004</v>
+        <v>0.5</v>
       </c>
       <c r="J23" s="1">
         <f t="shared" ca="1" si="14"/>
-        <v>0.53</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="K23" s="1">
         <f t="shared" ca="1" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>28</v>
       </c>
       <c r="C24" s="3">
         <f ca="1">AVERAGE(C4:C21)</f>
-        <v>7</v>
+        <v>8.2941176470588243</v>
       </c>
       <c r="D24" s="3">
         <f t="shared" ref="D24:E24" ca="1" si="15">AVERAGE(D4:D21)</f>
-        <v>16</v>
+        <v>15.764705882352942</v>
       </c>
       <c r="E24" s="3">
         <f t="shared" ca="1" si="15"/>
-        <v>75.588235294117652</v>
+        <v>76.588235294117652</v>
       </c>
       <c r="F24" s="3">
         <f t="shared" ref="F24" ca="1" si="16">AVERAGE(F4:F21)</f>
-        <v>0.41176470588235292</v>
+        <v>0.35294117647058826</v>
       </c>
       <c r="H24" s="1">
         <f ca="1">AVERAGE(H4:H21)</f>
-        <v>0.70000000000000007</v>
+        <v>0.8294117647058824</v>
       </c>
       <c r="I24" s="1">
         <f t="shared" ref="I24:K24" ca="1" si="17">AVERAGE(I4:I21)</f>
-        <v>0.79999999999999993</v>
+        <v>0.78823529411764703</v>
       </c>
       <c r="J24" s="1">
         <f t="shared" ca="1" si="17"/>
-        <v>0.75588235294117656</v>
+        <v>0.76588235294117635</v>
       </c>
       <c r="K24" s="1">
         <f t="shared" ca="1" si="17"/>
-        <v>0.41176470588235292</v>
+        <v>0.35294117647058826</v>
       </c>
     </row>
   </sheetData>
@@ -4786,309 +4785,309 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D419627-A140-48E5-ACCB-2DB7323EEF90}">
-  <dimension ref="B1:M12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:M8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="22.28515625" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" customWidth="1"/>
-    <col min="5" max="5" width="17.85546875" customWidth="1"/>
-    <col min="7" max="7" width="23.85546875" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" customWidth="1"/>
+    <col min="4" max="4" width="14.109375" customWidth="1"/>
+    <col min="5" max="5" width="17.88671875" customWidth="1"/>
+    <col min="7" max="7" width="23.88671875" customWidth="1"/>
     <col min="9" max="9" width="20" customWidth="1"/>
-    <col min="11" max="11" width="20.85546875" customWidth="1"/>
+    <col min="11" max="11" width="20.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B7" s="10" t="s">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B3" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C3" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D3" s="12">
         <v>3</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E3" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F3" s="13">
         <v>5</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="G3" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H3" s="14">
         <v>4</v>
       </c>
-      <c r="I7" s="14" t="s">
+      <c r="I3" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="J7" s="14">
+      <c r="J3" s="15">
         <v>3</v>
       </c>
-      <c r="K7" s="15" t="s">
+      <c r="K3" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="L7" s="15">
+      <c r="L3" s="16">
         <v>1</v>
       </c>
-      <c r="M7" s="10" t="s">
+      <c r="M3" s="11" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B8" s="16" t="s">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B4" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C4" s="4">
         <f ca="1">RANDBETWEEN(1, 5)</f>
-        <v>2</v>
-      </c>
-      <c r="D8" s="4">
-        <f ca="1">D$7*C8</f>
-        <v>6</v>
-      </c>
-      <c r="E8" s="5">
+        <v>5</v>
+      </c>
+      <c r="D4" s="4">
+        <f ca="1">D$3*C4</f>
+        <v>15</v>
+      </c>
+      <c r="E4" s="5">
         <f ca="1">RANDBETWEEN(1, 5)</f>
         <v>1</v>
       </c>
-      <c r="F8" s="5">
-        <f ca="1">F$7*E8</f>
+      <c r="F4" s="5">
+        <f ca="1">F$3*E4</f>
         <v>5</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G4" s="6">
         <f ca="1">RANDBETWEEN(1, 5)</f>
-        <v>5</v>
-      </c>
-      <c r="H8" s="6">
-        <f ca="1">H$7*G8</f>
-        <v>20</v>
-      </c>
-      <c r="I8" s="7">
+        <v>1</v>
+      </c>
+      <c r="H4" s="6">
+        <f ca="1">H$3*G4</f>
+        <v>4</v>
+      </c>
+      <c r="I4" s="7">
+        <f ca="1">RANDBETWEEN(1, 5)</f>
+        <v>4</v>
+      </c>
+      <c r="J4" s="7">
+        <f ca="1">J$3*I4</f>
+        <v>12</v>
+      </c>
+      <c r="K4" s="8">
         <f ca="1">RANDBETWEEN(1, 5)</f>
         <v>3</v>
       </c>
+      <c r="L4" s="8">
+        <f ca="1">L$3*K4</f>
+        <v>3</v>
+      </c>
+      <c r="M4" s="9">
+        <f ca="1">SUM(F4,D4,H4,J4,L4)</f>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B5" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="4">
+        <f t="shared" ref="C5:C8" ca="1" si="0">RANDBETWEEN(1, 5)</f>
+        <v>3</v>
+      </c>
+      <c r="D5" s="4">
+        <f t="shared" ref="D5:D8" ca="1" si="1">D$3*C5</f>
+        <v>9</v>
+      </c>
+      <c r="E5" s="5">
+        <f t="shared" ref="E5:E8" ca="1" si="2">RANDBETWEEN(1, 5)</f>
+        <v>1</v>
+      </c>
+      <c r="F5" s="5">
+        <f t="shared" ref="F5:F8" ca="1" si="3">F$3*E5</f>
+        <v>5</v>
+      </c>
+      <c r="G5" s="6">
+        <f t="shared" ref="G5:G8" ca="1" si="4">RANDBETWEEN(1, 5)</f>
+        <v>5</v>
+      </c>
+      <c r="H5" s="6">
+        <f t="shared" ref="H5:H8" ca="1" si="5">H$3*G5</f>
+        <v>20</v>
+      </c>
+      <c r="I5" s="7">
+        <f t="shared" ref="I5:I8" ca="1" si="6">RANDBETWEEN(1, 5)</f>
+        <v>4</v>
+      </c>
+      <c r="J5" s="7">
+        <f t="shared" ref="J5:J8" ca="1" si="7">J$3*I5</f>
+        <v>12</v>
+      </c>
+      <c r="K5" s="8">
+        <f t="shared" ref="K5:K8" ca="1" si="8">RANDBETWEEN(1, 5)</f>
+        <v>5</v>
+      </c>
+      <c r="L5" s="8">
+        <f t="shared" ref="L5:L8" ca="1" si="9">L$3*K5</f>
+        <v>5</v>
+      </c>
+      <c r="M5" s="9">
+        <f ca="1">SUM(F5,D5,H5,J5,L5)</f>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B6" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="4">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="D6" s="4">
+        <f t="shared" ca="1" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="E6" s="5">
+        <f t="shared" ca="1" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="F6" s="5">
+        <f t="shared" ca="1" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="G6" s="6">
+        <f t="shared" ca="1" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="H6" s="6">
+        <f t="shared" ca="1" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="I6" s="7">
+        <f t="shared" ca="1" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="J6" s="7">
+        <f t="shared" ca="1" si="7"/>
+        <v>12</v>
+      </c>
+      <c r="K6" s="8">
+        <f t="shared" ca="1" si="8"/>
+        <v>3</v>
+      </c>
+      <c r="L6" s="8">
+        <f t="shared" ca="1" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="M6" s="9">
+        <f t="shared" ref="M6" ca="1" si="10">SUM(F6,D6,H6,J6,L6)</f>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B7" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="4">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="D7" s="4">
+        <f t="shared" ca="1" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="E7" s="5">
+        <f t="shared" ca="1" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="F7" s="5">
+        <f t="shared" ca="1" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="G7" s="6">
+        <f t="shared" ca="1" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="H7" s="6">
+        <f t="shared" ca="1" si="5"/>
+        <v>16</v>
+      </c>
+      <c r="I7" s="7">
+        <f t="shared" ca="1" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="J7" s="7">
+        <f t="shared" ca="1" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="K7" s="8">
+        <f t="shared" ca="1" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="L7" s="8">
+        <f t="shared" ca="1" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="M7" s="9">
+        <f ca="1">SUM(F7,D7,H7,J7,L7)</f>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B8" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="4">
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D8" s="4">
+        <f t="shared" ca="1" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="E8" s="5">
+        <f t="shared" ca="1" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="F8" s="5">
+        <f t="shared" ca="1" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="G8" s="6">
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H8" s="6">
+        <f t="shared" ca="1" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="I8" s="7">
+        <f t="shared" ca="1" si="6"/>
+        <v>2</v>
+      </c>
       <c r="J8" s="7">
-        <f ca="1">J$7*I8</f>
-        <v>9</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>6</v>
       </c>
       <c r="K8" s="8">
-        <f ca="1">RANDBETWEEN(1, 5)</f>
-        <v>2</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>5</v>
       </c>
       <c r="L8" s="8">
-        <f ca="1">L$7*K8</f>
-        <v>2</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>5</v>
       </c>
       <c r="M8" s="9">
         <f ca="1">SUM(F8,D8,H8,J8,L8)</f>
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B9" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="4">
-        <f t="shared" ref="C9:C12" ca="1" si="0">RANDBETWEEN(1, 5)</f>
-        <v>4</v>
-      </c>
-      <c r="D9" s="4">
-        <f t="shared" ref="D9:D12" ca="1" si="1">D$7*C9</f>
-        <v>12</v>
-      </c>
-      <c r="E9" s="5">
-        <f t="shared" ref="E9:E12" ca="1" si="2">RANDBETWEEN(1, 5)</f>
-        <v>1</v>
-      </c>
-      <c r="F9" s="5">
-        <f t="shared" ref="F9:F12" ca="1" si="3">F$7*E9</f>
-        <v>5</v>
-      </c>
-      <c r="G9" s="6">
-        <f t="shared" ref="G9:G12" ca="1" si="4">RANDBETWEEN(1, 5)</f>
-        <v>3</v>
-      </c>
-      <c r="H9" s="6">
-        <f t="shared" ref="H9:H12" ca="1" si="5">H$7*G9</f>
-        <v>12</v>
-      </c>
-      <c r="I9" s="7">
-        <f t="shared" ref="I9:I12" ca="1" si="6">RANDBETWEEN(1, 5)</f>
-        <v>1</v>
-      </c>
-      <c r="J9" s="7">
-        <f t="shared" ref="J9:J12" ca="1" si="7">J$7*I9</f>
-        <v>3</v>
-      </c>
-      <c r="K9" s="8">
-        <f t="shared" ref="K9:L12" ca="1" si="8">RANDBETWEEN(1, 5)</f>
-        <v>4</v>
-      </c>
-      <c r="L9" s="8">
-        <f t="shared" ref="L9:L12" ca="1" si="9">L$7*K9</f>
-        <v>4</v>
-      </c>
-      <c r="M9" s="9">
-        <f ca="1">SUM(F9,D9,H9,J9,L9)</f>
         <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B10" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="4">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="D10" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="E10" s="5">
-        <f t="shared" ca="1" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="F10" s="5">
-        <f t="shared" ca="1" si="3"/>
-        <v>25</v>
-      </c>
-      <c r="G10" s="6">
-        <f t="shared" ca="1" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="H10" s="6">
-        <f t="shared" ca="1" si="5"/>
-        <v>4</v>
-      </c>
-      <c r="I10" s="7">
-        <f t="shared" ca="1" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="J10" s="7">
-        <f t="shared" ca="1" si="7"/>
-        <v>9</v>
-      </c>
-      <c r="K10" s="8">
-        <f t="shared" ca="1" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="L10" s="8">
-        <f t="shared" ca="1" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="M10" s="9">
-        <f t="shared" ref="M9:M12" ca="1" si="10">SUM(F10,D10,H10,J10,L10)</f>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B11" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="4">
-        <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D11" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="E11" s="5">
-        <f t="shared" ca="1" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="F11" s="5">
-        <f t="shared" ca="1" si="3"/>
-        <v>10</v>
-      </c>
-      <c r="G11" s="6">
-        <f t="shared" ca="1" si="4"/>
-        <v>4</v>
-      </c>
-      <c r="H11" s="6">
-        <f t="shared" ca="1" si="5"/>
-        <v>16</v>
-      </c>
-      <c r="I11" s="7">
-        <f t="shared" ca="1" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="J11" s="7">
-        <f t="shared" ca="1" si="7"/>
-        <v>6</v>
-      </c>
-      <c r="K11" s="8">
-        <f t="shared" ca="1" si="8"/>
-        <v>3</v>
-      </c>
-      <c r="L11" s="8">
-        <f t="shared" ca="1" si="9"/>
-        <v>3</v>
-      </c>
-      <c r="M11" s="9">
-        <f ca="1">SUM(F11,D11,H11,J11,L11)</f>
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B12" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="4">
-        <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="D12" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="E12" s="5">
-        <f t="shared" ca="1" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="F12" s="5">
-        <f t="shared" ca="1" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="G12" s="6">
-        <f t="shared" ca="1" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="H12" s="6">
-        <f t="shared" ca="1" si="5"/>
-        <v>20</v>
-      </c>
-      <c r="I12" s="7">
-        <f t="shared" ca="1" si="6"/>
-        <v>5</v>
-      </c>
-      <c r="J12" s="7">
-        <f t="shared" ca="1" si="7"/>
-        <v>15</v>
-      </c>
-      <c r="K12" s="8">
-        <f t="shared" ca="1" si="8"/>
-        <v>2</v>
-      </c>
-      <c r="L12" s="8">
-        <f t="shared" ca="1" si="9"/>
-        <v>2</v>
-      </c>
-      <c r="M12" s="9">
-        <f ca="1">SUM(F12,D12,H12,J12,L12)</f>
-        <v>51</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="M8:M12">
+  <conditionalFormatting sqref="M4:M8">
     <cfRule type="top10" dxfId="0" priority="1" percent="1" rank="10"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
